--- a/src/all/storage/src/build/resources/design/metadata/drives.xlsx
+++ b/src/all/storage/src/build/resources/design/metadata/drives.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/graham/Code/asystem/src/all/storage/src/build/resources/design/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C96A4ED-C195-9F49-8DCC-C85B7A184749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6029131F-8192-C14A-A69B-1F9D10EF5F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7060" yWindow="600" windowWidth="35700" windowHeight="24640" xr2:uid="{29B6FCDA-2052-C242-834F-5F308DA013F5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="143">
   <si>
     <t>Total</t>
   </si>
@@ -467,6 +467,9 @@
   </si>
   <si>
     <t>Baseline Write MB/s</t>
+  </si>
+  <si>
+    <t>Usage %</t>
   </si>
 </sst>
 </file>
@@ -808,6 +811,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -832,7 +836,6 @@
     <xf numFmtId="1" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1246,7 +1249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C1D6D0-38CE-B640-B89B-E1392BB57804}">
-  <dimension ref="A2:V19"/>
+  <dimension ref="A2:W19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
@@ -1262,10 +1265,11 @@
     <col min="12" max="12" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="64.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="42" t="s">
         <v>8</v>
       </c>
@@ -1312,125 +1316,130 @@
         <v>141</v>
       </c>
       <c r="Q2" s="54" t="s">
+        <v>142</v>
+      </c>
+      <c r="R2" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="R2" s="36"/>
       <c r="S2" s="36"/>
       <c r="T2" s="36"/>
       <c r="U2" s="36"/>
       <c r="V2" s="36"/>
-    </row>
-    <row r="3" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="64" t="s">
+      <c r="W2" s="36"/>
+    </row>
+    <row r="3" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="64" t="s">
+      <c r="H3" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="I3" s="64">
+      <c r="I3" s="56">
         <v>1250</v>
       </c>
-      <c r="J3" s="64" t="s">
+      <c r="J3" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="K3" s="64" t="s">
+      <c r="K3" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="L3" s="64" t="s">
+      <c r="L3" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="M3" s="64" t="s">
+      <c r="M3" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="N3" s="64" t="s">
+      <c r="N3" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="O3" s="64">
+      <c r="O3" s="56">
         <v>33</v>
       </c>
-      <c r="P3" s="64">
+      <c r="P3" s="56">
         <v>216</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="R3" s="36"/>
       <c r="S3" s="36"/>
       <c r="T3" s="36"/>
       <c r="U3" s="36"/>
       <c r="V3" s="36"/>
-    </row>
-    <row r="4" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="64" t="s">
+      <c r="W3" s="36"/>
+    </row>
+    <row r="4" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="E4" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="F4" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="I4" s="64">
+      <c r="I4" s="56">
         <v>1250</v>
       </c>
-      <c r="J4" s="64" t="s">
+      <c r="J4" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="64" t="s">
+      <c r="K4" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="L4" s="64" t="s">
+      <c r="L4" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="M4" s="64" t="s">
+      <c r="M4" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="N4" s="64" t="s">
+      <c r="N4" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="O4" s="64">
-        <v>27</v>
-      </c>
-      <c r="P4" s="64">
+      <c r="O4" s="56">
+        <v>52</v>
+      </c>
+      <c r="P4" s="56">
         <v>107</v>
       </c>
-      <c r="Q4" s="64" t="s">
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="R4" s="36"/>
       <c r="S4" s="36"/>
       <c r="T4" s="36"/>
       <c r="U4" s="36"/>
       <c r="V4" s="36"/>
-    </row>
-    <row r="5" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W4" s="36"/>
+    </row>
+    <row r="5" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="55" t="s">
         <v>17</v>
       </c>
@@ -1477,13 +1486,14 @@
         <v>119</v>
       </c>
       <c r="Q5" s="55"/>
-      <c r="R5" s="36"/>
+      <c r="R5" s="55"/>
       <c r="S5" s="36"/>
       <c r="T5" s="36"/>
       <c r="U5" s="36"/>
       <c r="V5" s="36"/>
-    </row>
-    <row r="6" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W5" s="36"/>
+    </row>
+    <row r="6" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="55" t="s">
         <v>14</v>
       </c>
@@ -1530,13 +1540,14 @@
         <v>214</v>
       </c>
       <c r="Q6" s="55"/>
-      <c r="R6" s="36"/>
+      <c r="R6" s="55"/>
       <c r="S6" s="36"/>
       <c r="T6" s="36"/>
       <c r="U6" s="36"/>
       <c r="V6" s="36"/>
-    </row>
-    <row r="7" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W6" s="36"/>
+    </row>
+    <row r="7" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="55" t="s">
         <v>58</v>
       </c>
@@ -1583,13 +1594,14 @@
         <v>238</v>
       </c>
       <c r="Q7" s="55"/>
-      <c r="R7" s="36"/>
+      <c r="R7" s="55"/>
       <c r="S7" s="36"/>
       <c r="T7" s="36"/>
       <c r="U7" s="36"/>
       <c r="V7" s="36"/>
-    </row>
-    <row r="8" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W7" s="36"/>
+    </row>
+    <row r="8" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="55" t="s">
         <v>12</v>
       </c>
@@ -1635,16 +1647,17 @@
       <c r="P8" s="55">
         <v>131</v>
       </c>
-      <c r="Q8" s="55" t="s">
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="R8" s="36"/>
       <c r="S8" s="36"/>
       <c r="T8" s="36"/>
       <c r="U8" s="36"/>
       <c r="V8" s="36"/>
-    </row>
-    <row r="9" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W8" s="36"/>
+    </row>
+    <row r="9" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="55" t="s">
         <v>13</v>
       </c>
@@ -1691,13 +1704,14 @@
         <v>141</v>
       </c>
       <c r="Q9" s="55"/>
-      <c r="R9" s="36"/>
+      <c r="R9" s="55"/>
       <c r="S9" s="36"/>
       <c r="T9" s="36"/>
       <c r="U9" s="36"/>
       <c r="V9" s="36"/>
-    </row>
-    <row r="10" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W9" s="36"/>
+    </row>
+    <row r="10" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="55" t="s">
         <v>65</v>
       </c>
@@ -1744,13 +1758,14 @@
         <v>143</v>
       </c>
       <c r="Q10" s="55"/>
-      <c r="R10" s="36"/>
+      <c r="R10" s="55"/>
       <c r="S10" s="36"/>
       <c r="T10" s="36"/>
       <c r="U10" s="36"/>
       <c r="V10" s="36"/>
-    </row>
-    <row r="11" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W10" s="36"/>
+    </row>
+    <row r="11" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="55" t="s">
         <v>9</v>
       </c>
@@ -1796,16 +1811,17 @@
       <c r="P11" s="55">
         <v>143</v>
       </c>
-      <c r="Q11" s="55" t="s">
+      <c r="Q11" s="55"/>
+      <c r="R11" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="R11" s="36"/>
       <c r="S11" s="36"/>
       <c r="T11" s="36"/>
       <c r="U11" s="36"/>
       <c r="V11" s="36"/>
-    </row>
-    <row r="12" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W11" s="36"/>
+    </row>
+    <row r="12" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="55" t="s">
         <v>10</v>
       </c>
@@ -1851,16 +1867,17 @@
       <c r="P12" s="55">
         <v>81</v>
       </c>
-      <c r="Q12" s="55" t="s">
+      <c r="Q12" s="55"/>
+      <c r="R12" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="R12" s="36"/>
       <c r="S12" s="36"/>
       <c r="T12" s="36"/>
       <c r="U12" s="36"/>
       <c r="V12" s="36"/>
-    </row>
-    <row r="13" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W12" s="36"/>
+    </row>
+    <row r="13" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="55" t="s">
         <v>59</v>
       </c>
@@ -1906,16 +1923,17 @@
       <c r="P13" s="55">
         <v>103</v>
       </c>
-      <c r="Q13" s="55" t="s">
+      <c r="Q13" s="55"/>
+      <c r="R13" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="R13" s="36"/>
       <c r="S13" s="36"/>
       <c r="T13" s="36"/>
       <c r="U13" s="36"/>
       <c r="V13" s="36"/>
-    </row>
-    <row r="14" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W13" s="36"/>
+    </row>
+    <row r="14" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
       <c r="D14" s="36"/>
@@ -1937,8 +1955,9 @@
       <c r="T14" s="36"/>
       <c r="U14" s="36"/>
       <c r="V14" s="36"/>
-    </row>
-    <row r="15" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W14" s="36"/>
+    </row>
+    <row r="15" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="36"/>
       <c r="C15" s="36"/>
       <c r="D15" s="36"/>
@@ -1960,8 +1979,9 @@
       <c r="T15" s="36"/>
       <c r="U15" s="36"/>
       <c r="V15" s="36"/>
-    </row>
-    <row r="16" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W15" s="36"/>
+    </row>
+    <row r="16" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
       <c r="D16" s="36"/>
@@ -1983,8 +2003,9 @@
       <c r="T16" s="36"/>
       <c r="U16" s="36"/>
       <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W16" s="36"/>
+    </row>
+    <row r="17" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
@@ -2006,8 +2027,9 @@
       <c r="T17" s="36"/>
       <c r="U17" s="36"/>
       <c r="V17" s="36"/>
-    </row>
-    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W17" s="36"/>
+    </row>
+    <row r="18" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="36"/>
       <c r="C18" s="36"/>
       <c r="D18" s="36"/>
@@ -2028,8 +2050,9 @@
       <c r="S18" s="36"/>
       <c r="T18" s="36"/>
       <c r="U18" s="36"/>
-    </row>
-    <row r="19" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="V18" s="36"/>
+    </row>
+    <row r="19" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="36"/>
       <c r="B19" s="36"/>
       <c r="C19" s="36"/>
@@ -2105,84 +2128,84 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:60" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56" t="s">
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
     </row>
     <row r="3" spans="2:60" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="58" t="s">
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="57" t="s">
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="T3" s="57"/>
+      <c r="T3" s="58"/>
     </row>
     <row r="4" spans="2:60" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="61" t="s">
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="63"/>
-      <c r="I4" s="56" t="s">
+      <c r="H4" s="64"/>
+      <c r="I4" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56" t="s">
+      <c r="J4" s="57"/>
+      <c r="K4" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="58" t="s">
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="59"/>
-      <c r="R4" s="59"/>
-      <c r="S4" s="59"/>
-      <c r="T4" s="60"/>
+      <c r="P4" s="60"/>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="61"/>
     </row>
     <row r="5" spans="2:60" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="21" t="s">

--- a/src/all/storage/src/build/resources/design/metadata/drives.xlsx
+++ b/src/all/storage/src/build/resources/design/metadata/drives.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/graham/Code/asystem/src/all/storage/src/build/resources/design/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6029131F-8192-C14A-A69B-1F9D10EF5F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3910A5C6-5C2A-6844-A41F-8EF0D12848B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7060" yWindow="600" windowWidth="35700" windowHeight="24640" xr2:uid="{29B6FCDA-2052-C242-834F-5F308DA013F5}"/>
   </bookViews>
@@ -1373,7 +1373,9 @@
       <c r="P3" s="56">
         <v>216</v>
       </c>
-      <c r="Q3" s="56"/>
+      <c r="Q3" s="56">
+        <v>73</v>
+      </c>
       <c r="R3" s="56" t="s">
         <v>101</v>
       </c>
@@ -1429,7 +1431,9 @@
       <c r="P4" s="56">
         <v>107</v>
       </c>
-      <c r="Q4" s="56"/>
+      <c r="Q4" s="56">
+        <v>58</v>
+      </c>
       <c r="R4" s="56" t="s">
         <v>110</v>
       </c>
@@ -1485,7 +1489,9 @@
       <c r="P5" s="55">
         <v>119</v>
       </c>
-      <c r="Q5" s="55"/>
+      <c r="Q5" s="55">
+        <v>63</v>
+      </c>
       <c r="R5" s="55"/>
       <c r="S5" s="36"/>
       <c r="T5" s="36"/>
@@ -1539,7 +1545,9 @@
       <c r="P6" s="55">
         <v>214</v>
       </c>
-      <c r="Q6" s="55"/>
+      <c r="Q6" s="55">
+        <v>51</v>
+      </c>
       <c r="R6" s="55"/>
       <c r="S6" s="36"/>
       <c r="T6" s="36"/>
@@ -1593,7 +1601,9 @@
       <c r="P7" s="55">
         <v>238</v>
       </c>
-      <c r="Q7" s="55"/>
+      <c r="Q7" s="55">
+        <v>60</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="36"/>
       <c r="T7" s="36"/>
@@ -1647,7 +1657,9 @@
       <c r="P8" s="55">
         <v>131</v>
       </c>
-      <c r="Q8" s="55"/>
+      <c r="Q8" s="55">
+        <v>53</v>
+      </c>
       <c r="R8" s="55" t="s">
         <v>126</v>
       </c>
@@ -1703,7 +1715,9 @@
       <c r="P9" s="55">
         <v>141</v>
       </c>
-      <c r="Q9" s="55"/>
+      <c r="Q9" s="55">
+        <v>57</v>
+      </c>
       <c r="R9" s="55"/>
       <c r="S9" s="36"/>
       <c r="T9" s="36"/>
@@ -1757,7 +1771,9 @@
       <c r="P10" s="55">
         <v>143</v>
       </c>
-      <c r="Q10" s="55"/>
+      <c r="Q10" s="55">
+        <v>75</v>
+      </c>
       <c r="R10" s="55"/>
       <c r="S10" s="36"/>
       <c r="T10" s="36"/>
@@ -1811,7 +1827,9 @@
       <c r="P11" s="55">
         <v>143</v>
       </c>
-      <c r="Q11" s="55"/>
+      <c r="Q11" s="55">
+        <v>80</v>
+      </c>
       <c r="R11" s="55" t="s">
         <v>126</v>
       </c>
@@ -1867,7 +1885,9 @@
       <c r="P12" s="55">
         <v>81</v>
       </c>
-      <c r="Q12" s="55"/>
+      <c r="Q12" s="55">
+        <v>77</v>
+      </c>
       <c r="R12" s="55" t="s">
         <v>136</v>
       </c>
@@ -1923,7 +1943,9 @@
       <c r="P13" s="55">
         <v>103</v>
       </c>
-      <c r="Q13" s="55"/>
+      <c r="Q13" s="55">
+        <v>75</v>
+      </c>
       <c r="R13" s="55" t="s">
         <v>136</v>
       </c>

--- a/src/all/storage/src/build/resources/design/metadata/drives.xlsx
+++ b/src/all/storage/src/build/resources/design/metadata/drives.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/graham/Code/asystem/src/all/storage/src/build/resources/design/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3910A5C6-5C2A-6844-A41F-8EF0D12848B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B942CC58-6A96-7542-81FE-936D89534FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7060" yWindow="600" windowWidth="35700" windowHeight="24640" xr2:uid="{29B6FCDA-2052-C242-834F-5F308DA013F5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="142">
   <si>
     <t>Total</t>
   </si>
@@ -310,9 +310,6 @@
     <t>NAND</t>
   </si>
   <si>
-    <t>TRIM</t>
-  </si>
-  <si>
     <t>Cache GB</t>
   </si>
   <si>
@@ -340,9 +337,6 @@
     <t>TLC</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>~200+</t>
   </si>
   <si>
@@ -400,9 +394,6 @@
     <t>1.8T</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>~100+</t>
   </si>
   <si>
@@ -470,6 +461,12 @@
   </si>
   <si>
     <t>Usage %</t>
+  </si>
+  <si>
+    <t>NQ710</t>
+  </si>
+  <si>
+    <t>NM790</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C1D6D0-38CE-B640-B89B-E1392BB57804}">
-  <dimension ref="A2:W19"/>
+  <dimension ref="A2:V19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
@@ -1263,13 +1260,12 @@
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="42" t="s">
         <v>8</v>
       </c>
@@ -1307,27 +1303,24 @@
         <v>89</v>
       </c>
       <c r="N2" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="O2" s="54" t="s">
+        <v>138</v>
+      </c>
+      <c r="P2" s="54" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q2" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="O2" s="54" t="s">
-        <v>140</v>
-      </c>
-      <c r="P2" s="54" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q2" s="54" t="s">
-        <v>142</v>
-      </c>
-      <c r="R2" s="54" t="s">
-        <v>91</v>
-      </c>
+      <c r="R2" s="36"/>
       <c r="S2" s="36"/>
       <c r="T2" s="36"/>
       <c r="U2" s="36"/>
       <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-    </row>
-    <row r="3" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="56" t="s">
         <v>15</v>
       </c>
@@ -1335,57 +1328,54 @@
         <v>19</v>
       </c>
       <c r="D3" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="56" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="G3" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="56" t="s">
+      <c r="H3" s="56" t="s">
         <v>94</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>95</v>
       </c>
       <c r="I3" s="56">
         <v>1250</v>
       </c>
       <c r="J3" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="K3" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="K3" s="56" t="s">
+      <c r="L3" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="L3" s="56" t="s">
+      <c r="M3" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="M3" s="56" t="s">
+      <c r="N3" s="56">
+        <v>85.5</v>
+      </c>
+      <c r="O3" s="56">
+        <v>531.29999999999995</v>
+      </c>
+      <c r="P3" s="56">
+        <v>73</v>
+      </c>
+      <c r="Q3" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="N3" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="O3" s="56">
-        <v>33</v>
-      </c>
-      <c r="P3" s="56">
-        <v>216</v>
-      </c>
-      <c r="Q3" s="56">
-        <v>73</v>
-      </c>
-      <c r="R3" s="56" t="s">
-        <v>101</v>
-      </c>
+      <c r="R3" s="36"/>
       <c r="S3" s="36"/>
       <c r="T3" s="36"/>
       <c r="U3" s="36"/>
       <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-    </row>
-    <row r="4" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="56" t="s">
         <v>16</v>
       </c>
@@ -1393,57 +1383,54 @@
         <v>20</v>
       </c>
       <c r="D4" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="G4" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="56" t="s">
-        <v>105</v>
-      </c>
       <c r="H4" s="56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I4" s="56">
         <v>1250</v>
       </c>
       <c r="J4" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="K4" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="L4" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="56" t="s">
+      <c r="M4" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="L4" s="56" t="s">
+      <c r="N4" s="56">
+        <v>109.8</v>
+      </c>
+      <c r="O4" s="56">
+        <v>218.2</v>
+      </c>
+      <c r="P4" s="56">
+        <v>58</v>
+      </c>
+      <c r="Q4" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="M4" s="56" t="s">
-        <v>99</v>
-      </c>
-      <c r="N4" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="O4" s="56">
-        <v>52</v>
-      </c>
-      <c r="P4" s="56">
-        <v>107</v>
-      </c>
-      <c r="Q4" s="56">
-        <v>58</v>
-      </c>
-      <c r="R4" s="56" t="s">
-        <v>110</v>
-      </c>
+      <c r="R4" s="36"/>
       <c r="S4" s="36"/>
       <c r="T4" s="36"/>
       <c r="U4" s="36"/>
       <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-    </row>
-    <row r="5" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="55" t="s">
         <v>17</v>
       </c>
@@ -1451,55 +1438,52 @@
         <v>28</v>
       </c>
       <c r="D5" s="55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F5" s="55" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G5" s="55" t="s">
         <v>4</v>
       </c>
       <c r="H5" s="55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I5" s="55">
         <v>1250</v>
       </c>
       <c r="J5" s="55" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K5" s="55" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L5" s="55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M5" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="N5" s="55" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="N5" s="55">
+        <v>434.4</v>
       </c>
       <c r="O5" s="55">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="P5" s="55">
-        <v>119</v>
-      </c>
-      <c r="Q5" s="55">
         <v>63</v>
       </c>
-      <c r="R5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="36"/>
       <c r="S5" s="36"/>
       <c r="T5" s="36"/>
       <c r="U5" s="36"/>
       <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-    </row>
-    <row r="6" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="55" t="s">
         <v>14</v>
       </c>
@@ -1507,55 +1491,52 @@
         <v>26</v>
       </c>
       <c r="D6" s="55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" s="55" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="F6" s="55" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G6" s="55" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H6" s="55" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I6" s="55">
         <v>3500</v>
       </c>
       <c r="J6" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="M6" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="K6" s="55" t="s">
-        <v>118</v>
-      </c>
-      <c r="L6" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="M6" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="N6" s="55" t="s">
-        <v>120</v>
+      <c r="N6" s="55">
+        <v>773.1</v>
       </c>
       <c r="O6" s="55">
-        <v>454</v>
+        <v>612.79999999999995</v>
       </c>
       <c r="P6" s="55">
-        <v>214</v>
-      </c>
-      <c r="Q6" s="55">
         <v>51</v>
       </c>
-      <c r="R6" s="55"/>
+      <c r="Q6" s="55"/>
+      <c r="R6" s="36"/>
       <c r="S6" s="36"/>
       <c r="T6" s="36"/>
       <c r="U6" s="36"/>
       <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-    </row>
-    <row r="7" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="55" t="s">
         <v>58</v>
       </c>
@@ -1563,55 +1544,52 @@
         <v>27</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E7" s="55" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G7" s="55" t="s">
         <v>4</v>
       </c>
       <c r="H7" s="55" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I7" s="55">
         <v>600</v>
       </c>
       <c r="J7" s="55" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K7" s="55" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="L7" s="55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M7" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="N7" s="55" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="N7" s="55">
+        <v>550.70000000000005</v>
       </c>
       <c r="O7" s="55">
-        <v>459</v>
+        <v>367.3</v>
       </c>
       <c r="P7" s="55">
-        <v>238</v>
-      </c>
-      <c r="Q7" s="55">
         <v>60</v>
       </c>
-      <c r="R7" s="55"/>
+      <c r="Q7" s="55"/>
+      <c r="R7" s="36"/>
       <c r="S7" s="36"/>
       <c r="T7" s="36"/>
       <c r="U7" s="36"/>
       <c r="V7" s="36"/>
-      <c r="W7" s="36"/>
-    </row>
-    <row r="8" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="55" t="s">
         <v>12</v>
       </c>
@@ -1619,57 +1597,54 @@
         <v>24</v>
       </c>
       <c r="D8" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="E8" s="55" t="s">
+      <c r="G8" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="F8" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="55" t="s">
-        <v>105</v>
-      </c>
       <c r="H8" s="55" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I8" s="55">
         <v>3500</v>
       </c>
       <c r="J8" s="55" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K8" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="L8" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="M8" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="L8" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="M8" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="N8" s="55" t="s">
-        <v>109</v>
+      <c r="N8" s="55">
+        <v>508</v>
       </c>
       <c r="O8" s="55">
-        <v>632</v>
+        <v>472.3</v>
       </c>
       <c r="P8" s="55">
-        <v>131</v>
-      </c>
-      <c r="Q8" s="55">
         <v>53</v>
       </c>
-      <c r="R8" s="55" t="s">
-        <v>126</v>
-      </c>
+      <c r="Q8" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="R8" s="36"/>
       <c r="S8" s="36"/>
       <c r="T8" s="36"/>
       <c r="U8" s="36"/>
       <c r="V8" s="36"/>
-      <c r="W8" s="36"/>
-    </row>
-    <row r="9" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="55" t="s">
         <v>13</v>
       </c>
@@ -1677,55 +1652,52 @@
         <v>25</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G9" s="55" t="s">
         <v>4</v>
       </c>
       <c r="H9" s="55" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I9" s="55">
         <v>600</v>
       </c>
       <c r="J9" s="55" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K9" s="55" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L9" s="55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M9" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="N9" s="55" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="N9" s="55">
+        <v>485.2</v>
       </c>
       <c r="O9" s="55">
-        <v>412</v>
+        <v>317.5</v>
       </c>
       <c r="P9" s="55">
-        <v>141</v>
-      </c>
-      <c r="Q9" s="55">
         <v>57</v>
       </c>
-      <c r="R9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="36"/>
       <c r="S9" s="36"/>
       <c r="T9" s="36"/>
       <c r="U9" s="36"/>
       <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-    </row>
-    <row r="10" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="55" t="s">
         <v>65</v>
       </c>
@@ -1733,55 +1705,54 @@
         <v>23</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F10" s="55" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G10" s="55" t="s">
         <v>4</v>
       </c>
       <c r="H10" s="55" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I10" s="55">
         <v>625</v>
       </c>
       <c r="J10" s="55" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K10" s="55" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L10" s="55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M10" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="N10" s="55" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="N10" s="55">
+        <v>454.9</v>
       </c>
       <c r="O10" s="55">
-        <v>256</v>
+        <v>30.3</v>
       </c>
       <c r="P10" s="55">
-        <v>143</v>
-      </c>
-      <c r="Q10" s="55">
         <v>75</v>
       </c>
-      <c r="R10" s="55"/>
+      <c r="Q10" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="R10" s="36"/>
       <c r="S10" s="36"/>
       <c r="T10" s="36"/>
       <c r="U10" s="36"/>
       <c r="V10" s="36"/>
-      <c r="W10" s="36"/>
-    </row>
-    <row r="11" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="55" t="s">
         <v>9</v>
       </c>
@@ -1789,57 +1760,54 @@
         <v>21</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E11" s="55" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F11" s="55" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G11" s="55" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H11" s="55" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I11" s="55">
         <v>3500</v>
       </c>
       <c r="J11" s="55" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K11" s="55" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L11" s="55" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M11" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="N11" s="55" t="s">
-        <v>135</v>
+        <v>132</v>
+      </c>
+      <c r="N11" s="55">
+        <v>566.79999999999995</v>
       </c>
       <c r="O11" s="55">
-        <v>612</v>
+        <v>716.2</v>
       </c>
       <c r="P11" s="55">
-        <v>143</v>
-      </c>
-      <c r="Q11" s="55">
         <v>80</v>
       </c>
-      <c r="R11" s="55" t="s">
-        <v>126</v>
-      </c>
+      <c r="Q11" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="R11" s="36"/>
       <c r="S11" s="36"/>
       <c r="T11" s="36"/>
       <c r="U11" s="36"/>
       <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-    </row>
-    <row r="12" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="55" t="s">
         <v>10</v>
       </c>
@@ -1847,57 +1815,52 @@
         <v>22</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G12" s="55" t="s">
         <v>4</v>
       </c>
       <c r="H12" s="55" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I12" s="55">
         <v>600</v>
       </c>
       <c r="J12" s="55" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K12" s="55" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L12" s="55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M12" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="N12" s="55" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="N12" s="55">
+        <v>486.8</v>
       </c>
       <c r="O12" s="55">
-        <v>406</v>
+        <v>277.5</v>
       </c>
       <c r="P12" s="55">
-        <v>81</v>
-      </c>
-      <c r="Q12" s="55">
         <v>77</v>
       </c>
-      <c r="R12" s="55" t="s">
-        <v>136</v>
-      </c>
+      <c r="Q12" s="55"/>
+      <c r="R12" s="36"/>
       <c r="S12" s="36"/>
       <c r="T12" s="36"/>
       <c r="U12" s="36"/>
       <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
-    </row>
-    <row r="13" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="55" t="s">
         <v>59</v>
       </c>
@@ -1905,57 +1868,54 @@
         <v>63</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E13" s="55" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F13" s="55" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G13" s="55" t="s">
         <v>4</v>
       </c>
       <c r="H13" s="55" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I13" s="55">
         <v>625</v>
       </c>
       <c r="J13" s="55" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K13" s="55" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L13" s="55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M13" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="55" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="N13" s="55">
+        <v>413.3</v>
       </c>
       <c r="O13" s="55">
-        <v>307</v>
+        <v>117.2</v>
       </c>
       <c r="P13" s="55">
-        <v>103</v>
-      </c>
-      <c r="Q13" s="55">
         <v>75</v>
       </c>
-      <c r="R13" s="55" t="s">
-        <v>136</v>
-      </c>
+      <c r="Q13" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="R13" s="36"/>
       <c r="S13" s="36"/>
       <c r="T13" s="36"/>
       <c r="U13" s="36"/>
       <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-    </row>
-    <row r="14" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
       <c r="D14" s="36"/>
@@ -1977,9 +1937,8 @@
       <c r="T14" s="36"/>
       <c r="U14" s="36"/>
       <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
-    </row>
-    <row r="15" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="36"/>
       <c r="C15" s="36"/>
       <c r="D15" s="36"/>
@@ -2001,9 +1960,8 @@
       <c r="T15" s="36"/>
       <c r="U15" s="36"/>
       <c r="V15" s="36"/>
-      <c r="W15" s="36"/>
-    </row>
-    <row r="16" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
       <c r="D16" s="36"/>
@@ -2025,9 +1983,8 @@
       <c r="T16" s="36"/>
       <c r="U16" s="36"/>
       <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
@@ -2049,9 +2006,8 @@
       <c r="T17" s="36"/>
       <c r="U17" s="36"/>
       <c r="V17" s="36"/>
-      <c r="W17" s="36"/>
-    </row>
-    <row r="18" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="36"/>
       <c r="C18" s="36"/>
       <c r="D18" s="36"/>
@@ -2072,9 +2028,8 @@
       <c r="S18" s="36"/>
       <c r="T18" s="36"/>
       <c r="U18" s="36"/>
-      <c r="V18" s="36"/>
-    </row>
-    <row r="19" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="36"/>
       <c r="B19" s="36"/>
       <c r="C19" s="36"/>
@@ -2089,7 +2044,6 @@
       <c r="L19" s="36"/>
       <c r="M19" s="36"/>
       <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/all/storage/src/build/resources/design/metadata/drives.xlsx
+++ b/src/all/storage/src/build/resources/design/metadata/drives.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/graham/Code/asystem/src/all/storage/src/build/resources/design/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B942CC58-6A96-7542-81FE-936D89534FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD60F89-F885-6146-9F4D-06A7A4A6EA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7060" yWindow="600" windowWidth="35700" windowHeight="24640" xr2:uid="{29B6FCDA-2052-C242-834F-5F308DA013F5}"/>
   </bookViews>

--- a/src/all/storage/src/build/resources/design/metadata/drives.xlsx
+++ b/src/all/storage/src/build/resources/design/metadata/drives.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/graham/Code/asystem/src/all/storage/src/build/resources/design/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD60F89-F885-6146-9F4D-06A7A4A6EA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A76015-249C-354B-AD90-A962FCD30151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7060" yWindow="600" windowWidth="35700" windowHeight="24640" xr2:uid="{29B6FCDA-2052-C242-834F-5F308DA013F5}"/>
+    <workbookView xWindow="7060" yWindow="600" windowWidth="35700" windowHeight="24640" activeTab="1" xr2:uid="{29B6FCDA-2052-C242-834F-5F308DA013F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Specs" sheetId="3" r:id="rId1"/>
